--- a/prius2/input/criterium_impact_v26-01-27.xlsx
+++ b/prius2/input/criterium_impact_v26-01-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bram_dhondt\Documents\GitHub\prius\prius2\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6789D0BF-B1D8-4865-A593-A37041203DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F9A98D-C50F-4F1D-9B6F-5DF0434F2E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="300">
   <si>
     <t>soort</t>
   </si>
@@ -943,7 +943,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -976,19 +976,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1040,7 +1027,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1048,20 +1035,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1069,15 +1047,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1094,23 +1063,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1122,7 +1084,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1355,7 +1322,7 @@
     <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -1373,7 +1340,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>297</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -1402,36 +1369,36 @@
       <c r="C2" s="1">
         <v>2979775</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>298</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
+      <c r="F2" s="10">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1">
-        <v>8848208</v>
-      </c>
-      <c r="D3" s="10" t="s">
+        <v>2978552</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E3" s="4">
@@ -1452,16 +1419,16 @@
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1">
-        <v>5217334</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>299</v>
+        <v>2489010</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -1481,15 +1448,15 @@
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>265</v>
       </c>
       <c r="C5" s="1">
-        <v>3084923</v>
-      </c>
-      <c r="D5" s="10" t="s">
+        <v>2489005</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E5" s="4">
@@ -1502,81 +1469,81 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1">
-        <v>2706080</v>
-      </c>
-      <c r="D6" s="10" t="s">
+        <v>1651430</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
       </c>
       <c r="I6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="C7" s="1">
-        <v>2394604</v>
-      </c>
-      <c r="D7" s="10" t="s">
+        <v>3190653</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1">
-        <v>5218823</v>
-      </c>
-      <c r="D8" s="10" t="s">
+        <v>2498252</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E8" s="4">
@@ -1592,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="I8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C9" s="1">
-        <v>2437282</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E9" s="13">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16">
-        <v>1</v>
+        <v>3084923</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C10" s="1">
-        <v>2427091</v>
-      </c>
-      <c r="D10" s="10" t="s">
+        <v>2340977</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E10" s="4">
@@ -1650,52 +1617,52 @@
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>2286388</v>
-      </c>
-      <c r="D11" s="10" t="s">
+        <v>9225458</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>9</v>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
-        <v>5219683</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E12" s="4">
+        <v>9448251</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="10">
         <v>1</v>
       </c>
       <c r="F12" s="4">
@@ -1707,21 +1674,21 @@
       <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="4">
-        <v>0</v>
+      <c r="I12" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C13" s="1">
-        <v>2390064</v>
-      </c>
-      <c r="D13" s="10" t="s">
+        <v>2706080</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E13" s="4">
@@ -1737,23 +1704,23 @@
         <v>0</v>
       </c>
       <c r="I13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1">
-        <v>9225458</v>
-      </c>
-      <c r="D14" s="10" t="s">
+        <v>5328593</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>1</v>
       </c>
       <c r="F14" s="4">
@@ -1762,27 +1729,27 @@
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
-        <v>1</v>
+      <c r="H14" s="10">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>209</v>
       </c>
       <c r="C15" s="1">
-        <v>9448251</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="13">
+        <v>2502792</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E15" s="4">
         <v>1</v>
       </c>
       <c r="F15" s="4">
@@ -1794,31 +1761,31 @@
       <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>130</v>
+        <v>288</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>289</v>
       </c>
       <c r="C16" s="1">
-        <v>2440934</v>
-      </c>
-      <c r="D16" s="10" t="s">
+        <v>3170247</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E16" s="4">
         <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4">
         <v>0</v>
@@ -1829,51 +1796,51 @@
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1">
-        <v>3169169</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E17" s="4">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>1</v>
+        <v>5187508</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1">
-        <v>1311477</v>
-      </c>
-      <c r="D18" s="10" t="s">
+        <v>2440934</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4">
         <v>1</v>
@@ -1887,16 +1854,16 @@
     </row>
     <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="C19" s="1">
-        <v>2367919</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>298</v>
+        <v>3129663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E19" s="4">
         <v>1</v>
@@ -1916,44 +1883,44 @@
     </row>
     <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1">
-        <v>10314173</v>
-      </c>
-      <c r="D20" s="10" t="s">
+        <v>2502938</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>298</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="F20" s="4">
-        <v>1</v>
+      <c r="F20" s="10">
+        <v>0</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <v>1</v>
-      </c>
-      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1">
-        <v>5871429</v>
-      </c>
-      <c r="D21" s="10" t="s">
+        <v>10314173</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>298</v>
       </c>
       <c r="E21" s="4">
@@ -1963,10 +1930,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="4">
         <v>1</v>
@@ -1974,28 +1941,28 @@
     </row>
     <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C22" s="1">
-        <v>1651430</v>
-      </c>
-      <c r="D22" s="10" t="s">
+        <v>5232437</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4">
         <v>1</v>
@@ -2003,22 +1970,22 @@
     </row>
     <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="C23" s="1">
-        <v>3189935</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>299</v>
+        <v>5361944</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
       </c>
       <c r="F23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
@@ -2026,28 +1993,28 @@
       <c r="H23" s="4">
         <v>0</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>141</v>
+        <v>283</v>
       </c>
       <c r="C24" s="1">
-        <v>4264680</v>
-      </c>
-      <c r="D24" s="10" t="s">
+        <v>2882443</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E24" s="4">
         <v>1</v>
       </c>
       <c r="F24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
@@ -2056,20 +2023,20 @@
         <v>1</v>
       </c>
       <c r="I24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C25" s="1">
-        <v>2362868</v>
-      </c>
-      <c r="D25" s="10" t="s">
+        <v>2437394</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E25" s="4">
@@ -2082,26 +2049,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>263</v>
       </c>
       <c r="C26" s="1">
-        <v>2928835</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E26" s="13">
+        <v>2437399</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26" s="4">
         <v>1</v>
       </c>
       <c r="F26" s="4">
@@ -2111,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4">
         <v>0</v>
@@ -2119,16 +2086,16 @@
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="C27" s="1">
-        <v>8930656</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>298</v>
+        <v>3189935</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E27" s="4">
         <v>1</v>
@@ -2140,26 +2107,26 @@
         <v>0</v>
       </c>
       <c r="H27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="C28" s="1">
-        <v>2226990</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E28" s="4">
+        <v>3084842</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" s="10">
         <v>1</v>
       </c>
       <c r="F28" s="4">
@@ -2168,10 +2135,10 @@
       <c r="G28" s="4">
         <v>0</v>
       </c>
-      <c r="H28" s="4">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4">
+      <c r="H28" s="10">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14">
         <v>1</v>
       </c>
     </row>
@@ -2185,7 +2152,7 @@
       <c r="C29" s="1">
         <v>2439838</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="7" t="s">
         <v>298</v>
       </c>
       <c r="E29" s="4">
@@ -2200,21 +2167,21 @@
       <c r="H29" s="4">
         <v>1</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C30" s="1">
-        <v>5232437</v>
-      </c>
-      <c r="D30" s="10" t="s">
+        <v>3169169</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E30" s="4">
@@ -2227,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -2235,18 +2202,18 @@
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="C31" s="1">
-        <v>5389029</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E31" s="13">
+        <v>5828232</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
       <c r="F31" s="4">
@@ -2258,33 +2225,33 @@
       <c r="H31" s="4">
         <v>0</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1">
-        <v>2440946</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>299</v>
+        <v>2440954</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4">
-        <v>1</v>
-      </c>
-      <c r="H32" s="4">
+      <c r="F32" s="10">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10">
         <v>0</v>
       </c>
       <c r="I32" s="4">
@@ -2293,15 +2260,15 @@
     </row>
     <row r="33" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="C33" s="1">
-        <v>8114276</v>
-      </c>
-      <c r="D33" s="10" t="s">
+        <v>4284921</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E33" s="4">
@@ -2317,23 +2284,23 @@
         <v>0</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C34" s="1">
-        <v>5220435</v>
-      </c>
-      <c r="D34" s="10" t="s">
+        <v>4417558</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="4">
         <v>1</v>
       </c>
       <c r="F34" s="4">
@@ -2343,24 +2310,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>0</v>
-      </c>
-      <c r="I34" s="17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1">
-        <v>2225776</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>299</v>
+        <v>9738098</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -2372,24 +2339,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="4">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1">
-        <v>9738098</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>298</v>
+        <v>2704521</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -2403,140 +2370,140 @@
       <c r="H36" s="4">
         <v>0</v>
       </c>
-      <c r="I36" s="13">
-        <v>1</v>
+      <c r="I36" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>183</v>
       </c>
       <c r="C37" s="1">
-        <v>5220136</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E37" s="17">
-        <v>1</v>
-      </c>
-      <c r="F37" s="16">
-        <v>0</v>
-      </c>
-      <c r="G37" s="17">
-        <v>1</v>
-      </c>
-      <c r="H37" s="16">
-        <v>0</v>
-      </c>
-      <c r="I37" s="17">
-        <v>1</v>
+        <v>2482499</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="s">
-        <v>35</v>
+      <c r="A38" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="C38" s="1">
-        <v>3134183</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>298</v>
+        <v>5362054</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
       </c>
-      <c r="F38" s="16">
-        <v>1</v>
+      <c r="F38" s="4">
+        <v>0</v>
       </c>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="C39" s="1">
-        <v>1315391</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E39" s="4">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4">
-        <v>0</v>
-      </c>
-      <c r="H39" s="4">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4">
+        <v>5220136</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E39" s="14">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13">
+        <v>0</v>
+      </c>
+      <c r="I39" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>36</v>
+      <c r="A40" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C40" s="1">
-        <v>5329260</v>
-      </c>
-      <c r="D40" s="10" t="s">
+        <v>3134183</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E40" s="13">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4">
-        <v>0</v>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="13">
+        <v>1</v>
       </c>
       <c r="G40" s="4">
         <v>0</v>
       </c>
-      <c r="H40" s="13">
-        <v>1</v>
-      </c>
-      <c r="I40" s="13">
-        <v>1</v>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1">
-        <v>5828232</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E41" s="4">
+        <v>5329260</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E41" s="10">
         <v>1</v>
       </c>
       <c r="F41" s="4">
@@ -2545,24 +2512,24 @@
       <c r="G41" s="4">
         <v>0</v>
       </c>
-      <c r="H41" s="4">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4">
-        <v>0</v>
+      <c r="H41" s="10">
+        <v>1</v>
+      </c>
+      <c r="I41" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>156</v>
+        <v>244</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="C42" s="1">
-        <v>8971201</v>
-      </c>
-      <c r="D42" s="10" t="s">
+        <v>2702865</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E42" s="4">
@@ -2575,52 +2542,52 @@
         <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C43" s="1">
-        <v>7346102</v>
-      </c>
-      <c r="D43" s="10" t="s">
+        <v>8889878</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="10">
         <v>1</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="4">
-        <v>0</v>
+      <c r="G43" s="10">
+        <v>1</v>
       </c>
       <c r="H43" s="4">
         <v>0</v>
       </c>
-      <c r="I43" s="4">
-        <v>0</v>
+      <c r="I43" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="C44" s="1">
-        <v>4033648</v>
-      </c>
-      <c r="D44" s="10" t="s">
+        <v>5329212</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E44" s="4">
@@ -2633,26 +2600,26 @@
         <v>0</v>
       </c>
       <c r="H44" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C45" s="1">
-        <v>2227289</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E45" s="13">
+        <v>2225776</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E45" s="4">
         <v>1</v>
       </c>
       <c r="F45" s="4">
@@ -2664,51 +2631,51 @@
       <c r="H45" s="4">
         <v>1</v>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="C46" s="1">
-        <v>7965247</v>
-      </c>
-      <c r="D46" s="10" t="s">
+        <v>7346102</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>9</v>
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="C47" s="1">
-        <v>8909595</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>299</v>
+        <v>8930656</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E47" s="4">
         <v>1</v>
@@ -2728,18 +2695,18 @@
     </row>
     <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="C48" s="1">
-        <v>2984306</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E48" s="4">
+        <v>8721209</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E48" s="10">
         <v>1</v>
       </c>
       <c r="F48" s="4">
@@ -2752,20 +2719,20 @@
         <v>1</v>
       </c>
       <c r="I48" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C49" s="1">
-        <v>9799308</v>
-      </c>
-      <c r="D49" s="10" t="s">
+        <v>8909595</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E49" s="4">
@@ -2775,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="4">
         <v>1</v>
@@ -2786,16 +2753,16 @@
     </row>
     <row r="50" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>43</v>
+        <v>239</v>
       </c>
       <c r="C50" s="1">
-        <v>4417558</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>298</v>
+        <v>8979506</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E50" s="4">
         <v>1</v>
@@ -2815,15 +2782,15 @@
     </row>
     <row r="51" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C51" s="1">
-        <v>5855350</v>
-      </c>
-      <c r="D51" s="10" t="s">
+        <v>8971201</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E51" s="4">
@@ -2839,20 +2806,20 @@
         <v>1</v>
       </c>
       <c r="I51" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="C52" s="1">
-        <v>5219681</v>
-      </c>
-      <c r="D52" s="10" t="s">
+        <v>5712056</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E52" s="4">
@@ -2868,26 +2835,26 @@
         <v>0</v>
       </c>
       <c r="I52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
+        <v>284</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="C53" s="1">
-        <v>8790531</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E53" s="13">
-        <v>1</v>
-      </c>
-      <c r="F53" s="16">
+        <v>2350580</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4">
         <v>0</v>
       </c>
       <c r="G53" s="4">
@@ -2896,24 +2863,24 @@
       <c r="H53" s="4">
         <v>0</v>
       </c>
-      <c r="I53" s="13">
+      <c r="I53" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>218</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>47</v>
+        <v>219</v>
       </c>
       <c r="C54" s="1">
-        <v>5229055</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E54" s="13">
+        <v>2350570</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E54" s="4">
         <v>1</v>
       </c>
       <c r="F54" s="4">
@@ -2925,50 +2892,50 @@
       <c r="H54" s="4">
         <v>0</v>
       </c>
-      <c r="I54" s="17">
+      <c r="I54" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="C55" s="1">
-        <v>8701771</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>298</v>
+        <v>2984306</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E55" s="4">
         <v>1</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="4">
         <v>0</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" s="4">
-        <v>0</v>
-      </c>
-      <c r="I55" s="17">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="I55" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>171</v>
+        <v>253</v>
       </c>
       <c r="C56" s="1">
-        <v>5274863</v>
-      </c>
-      <c r="D56" s="10" t="s">
+        <v>6063677</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E56" s="4">
@@ -2989,15 +2956,15 @@
     </row>
     <row r="57" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C57" s="1">
-        <v>7978544</v>
-      </c>
-      <c r="D57" s="10" t="s">
+        <v>7287606</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E57" s="4">
@@ -3010,36 +2977,36 @@
         <v>0</v>
       </c>
       <c r="H57" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="C58" s="1">
-        <v>7287606</v>
-      </c>
-      <c r="D58" s="10" t="s">
+        <v>3034825</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E58" s="4">
         <v>1</v>
       </c>
       <c r="F58" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4">
         <v>0</v>
@@ -3047,73 +3014,73 @@
     </row>
     <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>51</v>
+        <v>227</v>
       </c>
       <c r="C59" s="1">
-        <v>2479226</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E59" s="13">
+        <v>3628745</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" s="4">
         <v>1</v>
       </c>
       <c r="F59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="4">
         <v>0</v>
       </c>
       <c r="H59" s="4">
-        <v>0</v>
-      </c>
-      <c r="I59" s="16">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>52</v>
+        <v>256</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>53</v>
+        <v>257</v>
       </c>
       <c r="C60" s="1">
-        <v>2502938</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>298</v>
+        <v>3642949</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="F60" s="13">
-        <v>0</v>
+      <c r="F60" s="4">
+        <v>1</v>
       </c>
       <c r="G60" s="4">
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>0</v>
-      </c>
-      <c r="I60" s="17">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C61" s="1">
-        <v>2480764</v>
-      </c>
-      <c r="D61" s="10" t="s">
+        <v>2434271</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E61" s="4">
@@ -3134,28 +3101,28 @@
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="C62" s="1">
-        <v>3190653</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E62" s="4">
+        <v>5384931</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E62" s="10">
         <v>1</v>
       </c>
       <c r="F62" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="4">
         <v>0</v>
@@ -3163,22 +3130,22 @@
     </row>
     <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="C63" s="1">
-        <v>2704521</v>
-      </c>
-      <c r="D63" s="10" t="s">
+        <v>2984537</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E63" s="4">
         <v>1</v>
       </c>
       <c r="F63" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
@@ -3192,21 +3159,21 @@
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C64" s="1">
-        <v>3084842</v>
-      </c>
-      <c r="D64" s="10" t="s">
+        <v>5304257</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E64" s="13">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4">
+      <c r="E64" s="10">
+        <v>1</v>
+      </c>
+      <c r="F64" s="10">
         <v>0</v>
       </c>
       <c r="G64" s="4">
@@ -3215,53 +3182,53 @@
       <c r="H64" s="4">
         <v>0</v>
       </c>
-      <c r="I64" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="25" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="B65" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C65" s="22">
-        <v>2482499</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="E65" s="24">
-        <v>1</v>
-      </c>
-      <c r="F65" s="24">
-        <v>0</v>
-      </c>
-      <c r="G65" s="24">
-        <v>0</v>
-      </c>
-      <c r="H65" s="24">
-        <v>0</v>
-      </c>
-      <c r="I65" s="24">
+      <c r="I64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5304294</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E65" s="10">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4">
+        <v>0</v>
+      </c>
+      <c r="H65" s="4">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C66" s="1">
-        <v>5304294</v>
-      </c>
-      <c r="D66" s="10" t="s">
+        <v>11055820</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="10">
         <v>1</v>
       </c>
       <c r="F66" s="4">
@@ -3270,27 +3237,27 @@
       <c r="G66" s="4">
         <v>0</v>
       </c>
-      <c r="H66" s="4">
-        <v>0</v>
+      <c r="H66" s="10">
+        <v>1</v>
       </c>
       <c r="I66" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="C67" s="1">
-        <v>11055820</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E67" s="13">
+        <v>7978544</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
       <c r="F67" s="4">
@@ -3299,7 +3266,7 @@
       <c r="G67" s="4">
         <v>0</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="4">
         <v>1</v>
       </c>
       <c r="I67" s="4">
@@ -3308,15 +3275,15 @@
     </row>
     <row r="68" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="C68" s="1">
-        <v>2434271</v>
-      </c>
-      <c r="D68" s="10" t="s">
+        <v>2891770</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E68" s="4">
@@ -3329,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="4">
         <v>0</v>
@@ -3337,18 +3304,18 @@
     </row>
     <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="C69" s="1">
-        <v>3088310</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E69" s="13">
+        <v>8848208</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" s="4">
         <v>1</v>
       </c>
       <c r="F69" s="4">
@@ -3361,20 +3328,20 @@
         <v>0</v>
       </c>
       <c r="I69" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>186</v>
+        <v>268</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="C70" s="1">
-        <v>5289808</v>
-      </c>
-      <c r="D70" s="10" t="s">
+        <v>2865565</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E70" s="4">
@@ -3387,52 +3354,52 @@
         <v>0</v>
       </c>
       <c r="H70" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="C71" s="1">
-        <v>2863941</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="H71" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>9</v>
+        <v>9799308</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>189</v>
+        <v>291</v>
       </c>
       <c r="C72" s="1">
-        <v>2889173</v>
-      </c>
-      <c r="D72" s="10" t="s">
+        <v>2394486</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E72" s="4">
@@ -3442,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="G72" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4">
         <v>1</v>
@@ -3453,15 +3420,15 @@
     </row>
     <row r="73" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="C73" s="1">
-        <v>2650436</v>
-      </c>
-      <c r="D73" s="10" t="s">
+        <v>8114276</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E73" s="4">
@@ -3482,15 +3449,15 @@
     </row>
     <row r="74" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1">
-        <v>4038485</v>
-      </c>
-      <c r="D74" s="10" t="s">
+        <v>5855350</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E74" s="4">
@@ -3500,58 +3467,58 @@
         <v>0</v>
       </c>
       <c r="G74" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="4">
         <v>1</v>
       </c>
       <c r="I74" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C75" s="1">
-        <v>5328593</v>
-      </c>
-      <c r="D75" s="10" t="s">
+        <v>8790531</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E75" s="13">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4">
+      <c r="E75" s="10">
+        <v>1</v>
+      </c>
+      <c r="F75" s="13">
         <v>0</v>
       </c>
       <c r="G75" s="4">
         <v>0</v>
       </c>
-      <c r="H75" s="13">
-        <v>1</v>
-      </c>
-      <c r="I75" s="4">
-        <v>0</v>
+      <c r="H75" s="4">
+        <v>0</v>
+      </c>
+      <c r="I75" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="C76" s="1">
-        <v>8721209</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E76" s="13">
+        <v>2427091</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
       <c r="F76" s="4">
@@ -3561,23 +3528,23 @@
         <v>0</v>
       </c>
       <c r="H76" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="C77" s="1">
-        <v>5420991</v>
-      </c>
-      <c r="D77" s="10" t="s">
+        <v>5421039</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E77" s="4">
@@ -3598,15 +3565,15 @@
     </row>
     <row r="78" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C78" s="1">
-        <v>2977647</v>
-      </c>
-      <c r="D78" s="10" t="s">
+        <v>5420991</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E78" s="4">
@@ -3619,26 +3586,26 @@
         <v>0</v>
       </c>
       <c r="H78" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C79" s="1">
-        <v>2489010</v>
-      </c>
-      <c r="D79" s="10" t="s">
+        <v>2928835</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="10">
         <v>1</v>
       </c>
       <c r="F79" s="4">
@@ -3647,8 +3614,8 @@
       <c r="G79" s="4">
         <v>0</v>
       </c>
-      <c r="H79" s="4">
-        <v>0</v>
+      <c r="H79" s="10">
+        <v>1</v>
       </c>
       <c r="I79" s="4">
         <v>0</v>
@@ -3656,18 +3623,18 @@
     </row>
     <row r="80" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="C80" s="1">
-        <v>5389017</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E80" s="13">
+        <v>2650436</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
       <c r="F80" s="4">
@@ -3685,18 +3652,18 @@
     </row>
     <row r="81" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="C81" s="1">
-        <v>5384932</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E81" s="13">
+        <v>2869311</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
       <c r="F81" s="4">
@@ -3714,16 +3681,16 @@
     </row>
     <row r="82" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="C82" s="1">
-        <v>2443002</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>299</v>
+        <v>2292586</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E82" s="4">
         <v>1</v>
@@ -3743,45 +3710,45 @@
     </row>
     <row r="83" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C83" s="1">
-        <v>10919373</v>
-      </c>
-      <c r="D83" s="10" t="s">
+        <v>8458912</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E83" s="13">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
-        <v>0</v>
-      </c>
-      <c r="H83" s="17">
-        <v>1</v>
-      </c>
-      <c r="I83" s="13">
+      <c r="E83" s="10">
+        <v>1</v>
+      </c>
+      <c r="F83" s="10">
+        <v>0</v>
+      </c>
+      <c r="G83" s="10">
+        <v>0</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0</v>
+      </c>
+      <c r="I83" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="C84" s="1">
-        <v>2292586</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>298</v>
+        <v>5289808</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E84" s="4">
         <v>1</v>
@@ -3801,131 +3768,131 @@
     </row>
     <row r="85" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="C85" s="1">
-        <v>9442269</v>
-      </c>
-      <c r="D85" s="10" t="s">
+        <v>2367919</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="19" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2367913</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E85" s="4">
-        <v>1</v>
-      </c>
-      <c r="F85" s="4">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4">
-        <v>0</v>
-      </c>
-      <c r="H85" s="4">
-        <v>1</v>
-      </c>
-      <c r="I85" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" s="26" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B86" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="C86" s="18">
-        <v>5358460</v>
-      </c>
-      <c r="D86" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="E86" s="20">
-        <v>1</v>
-      </c>
-      <c r="F86" s="20">
-        <v>0</v>
-      </c>
-      <c r="G86" s="20">
-        <v>0</v>
-      </c>
-      <c r="H86" s="20">
-        <v>0</v>
-      </c>
-      <c r="I86" s="20">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C87" s="1">
-        <v>8458912</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>9</v>
+        <v>2394604</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C88" s="1">
-        <v>5384931</v>
-      </c>
-      <c r="D88" s="10" t="s">
+        <v>2286388</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="4">
-        <v>0</v>
-      </c>
-      <c r="G88" s="4">
-        <v>0</v>
-      </c>
-      <c r="H88" s="4">
-        <v>0</v>
-      </c>
-      <c r="I88" s="4">
-        <v>0</v>
+      <c r="F88" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="C89" s="1">
-        <v>2869311</v>
-      </c>
-      <c r="D89" s="10" t="s">
+        <v>2440946</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E89" s="4">
@@ -3935,30 +3902,30 @@
         <v>0</v>
       </c>
       <c r="G89" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="4">
         <v>0</v>
       </c>
       <c r="I89" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C90" s="1">
-        <v>2766030</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>9</v>
+        <v>5218823</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E90" s="4">
+        <v>1</v>
       </c>
       <c r="F90" s="4">
         <v>0</v>
@@ -3983,11 +3950,11 @@
       <c r="C91" s="1">
         <v>2479407</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>9</v>
+      <c r="E91" s="10">
+        <v>1</v>
       </c>
       <c r="F91" s="4">
         <v>0</v>
@@ -4004,51 +3971,51 @@
     </row>
     <row r="92" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C92" s="1">
-        <v>5712056</v>
-      </c>
-      <c r="D92" s="10" t="s">
+        <v>4264680</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E92" s="4">
         <v>1</v>
       </c>
       <c r="F92" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="4">
         <v>0</v>
       </c>
       <c r="H92" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C93" s="1">
-        <v>5219858</v>
-      </c>
-      <c r="D93" s="10" t="s">
+        <v>5361785</v>
+      </c>
+      <c r="D93" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E93" s="4">
         <v>1</v>
       </c>
       <c r="F93" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="4">
         <v>0</v>
@@ -4057,78 +4024,78 @@
         <v>1</v>
       </c>
       <c r="I93" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="C94" s="1">
-        <v>5892137</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>298</v>
+        <v>5361762</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E94" s="4">
         <v>1</v>
       </c>
       <c r="F94" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="4">
         <v>0</v>
       </c>
       <c r="H94" s="4">
-        <v>0</v>
-      </c>
-      <c r="I94" s="6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I94" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="C95" s="1">
-        <v>2502792</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E95" s="4">
-        <v>1</v>
-      </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-      <c r="G95" s="4">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4">
-        <v>0</v>
-      </c>
-      <c r="I95" s="4">
-        <v>1</v>
+        <v>2863941</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C96" s="1">
-        <v>2498252</v>
-      </c>
-      <c r="D96" s="10" t="s">
+        <v>2433536</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E96" s="4">
@@ -4144,55 +4111,55 @@
         <v>0</v>
       </c>
       <c r="I96" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>86</v>
+        <v>272</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>87</v>
+        <v>273</v>
       </c>
       <c r="C97" s="1">
-        <v>5187508</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G97" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I97" s="13" t="s">
-        <v>9</v>
+        <v>2434552</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="C98" s="1">
-        <v>2367913</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>299</v>
+        <v>8701771</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E98" s="4">
         <v>1</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="10">
         <v>0</v>
       </c>
       <c r="G98" s="4">
@@ -4201,50 +4168,50 @@
       <c r="H98" s="4">
         <v>0</v>
       </c>
-      <c r="I98" s="4">
-        <v>0</v>
+      <c r="I98" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C99" s="1">
-        <v>4284921</v>
-      </c>
-      <c r="D99" s="10" t="s">
+        <v>5219858</v>
+      </c>
+      <c r="D99" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E99" s="4">
         <v>1</v>
       </c>
       <c r="F99" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="4">
         <v>0</v>
       </c>
       <c r="H99" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1">
-        <v>5361762</v>
-      </c>
-      <c r="D100" s="10" t="s">
+        <v>2498305</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E100" s="4">
@@ -4257,23 +4224,23 @@
         <v>0</v>
       </c>
       <c r="H100" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>218</v>
+        <v>144</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>145</v>
       </c>
       <c r="C101" s="1">
-        <v>2350570</v>
-      </c>
-      <c r="D101" s="10" t="s">
+        <v>2226990</v>
+      </c>
+      <c r="D101" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E101" s="4">
@@ -4286,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="4">
         <v>1</v>
@@ -4294,15 +4261,15 @@
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="C102" s="1">
-        <v>2984537</v>
-      </c>
-      <c r="D102" s="10" t="s">
+        <v>3086784</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E102" s="4">
@@ -4318,23 +4285,23 @@
         <v>0</v>
       </c>
       <c r="I102" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>222</v>
+        <v>30</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>223</v>
+        <v>31</v>
       </c>
       <c r="C103" s="1">
-        <v>2437394</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E103" s="4">
+        <v>5220435</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E103" s="10">
         <v>1</v>
       </c>
       <c r="F103" s="4">
@@ -4344,30 +4311,30 @@
         <v>0</v>
       </c>
       <c r="H103" s="4">
-        <v>1</v>
-      </c>
-      <c r="I103" s="4">
+        <v>0</v>
+      </c>
+      <c r="I103" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C104" s="1">
-        <v>5361944</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>298</v>
+        <v>2390064</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E104" s="4">
         <v>1</v>
       </c>
       <c r="F104" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="4">
         <v>0</v>
@@ -4375,21 +4342,21 @@
       <c r="H104" s="4">
         <v>0</v>
       </c>
-      <c r="I104" s="5">
+      <c r="I104" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="C105" s="1">
-        <v>5361785</v>
-      </c>
-      <c r="D105" s="10" t="s">
+        <v>4033648</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E105" s="4">
@@ -4402,56 +4369,56 @@
         <v>0</v>
       </c>
       <c r="H105" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>226</v>
+        <v>59</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="C106" s="1">
-        <v>3628745</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E106" s="4">
+        <v>3088310</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E106" s="10">
         <v>1</v>
       </c>
       <c r="F106" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="4">
         <v>0</v>
       </c>
-      <c r="H106" s="4">
+      <c r="H106" s="10">
         <v>1</v>
       </c>
       <c r="I106" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>90</v>
+        <v>278</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>91</v>
+        <v>279</v>
       </c>
       <c r="C107" s="1">
-        <v>8889878</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>9</v>
+        <v>2870583</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1</v>
       </c>
       <c r="F107" s="4">
         <v>0</v>
@@ -4460,38 +4427,38 @@
         <v>0</v>
       </c>
       <c r="H107" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C108" s="1">
-        <v>2227231</v>
-      </c>
-      <c r="D108" s="10" t="s">
+        <v>5892137</v>
+      </c>
+      <c r="D108" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E108" s="13">
-        <v>1</v>
-      </c>
-      <c r="F108" s="4">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="10">
         <v>0</v>
       </c>
       <c r="G108" s="4">
         <v>0</v>
       </c>
       <c r="H108" s="4">
-        <v>1</v>
-      </c>
-      <c r="I108" s="4">
+        <v>0</v>
+      </c>
+      <c r="I108" s="10">
         <v>1</v>
       </c>
       <c r="K108" s="4"/>
@@ -4502,51 +4469,51 @@
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1">
-        <v>2891770</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E109" s="4">
-        <v>1</v>
-      </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4">
-        <v>0</v>
-      </c>
-      <c r="H109" s="4">
-        <v>1</v>
-      </c>
-      <c r="I109" s="4">
-        <v>0</v>
+        <v>7965247</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="C110" s="1">
-        <v>3034825</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E110" s="4">
+        <v>8946295</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E110" s="10">
         <v>1</v>
       </c>
       <c r="F110" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -4555,49 +4522,49 @@
         <v>1</v>
       </c>
       <c r="I110" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" s="19" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C111" s="1">
-        <v>3003979</v>
-      </c>
-      <c r="D111" s="10" t="s">
+        <v>2766030</v>
+      </c>
+      <c r="D111" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" s="7">
-        <v>0</v>
-      </c>
-      <c r="G111" s="5">
-        <v>1</v>
+      <c r="E111" s="10">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4">
+        <v>0</v>
       </c>
       <c r="H111" s="4">
         <v>0</v>
       </c>
-      <c r="I111" s="5">
+      <c r="I111" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="C112" s="1">
-        <v>2227300</v>
-      </c>
-      <c r="D112" s="10" t="s">
+        <v>2765942</v>
+      </c>
+      <c r="D112" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E112" s="4">
@@ -4618,18 +4585,18 @@
     </row>
     <row r="113" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="C113" s="1">
-        <v>2433536</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E113" s="4">
+        <v>2227289</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E113" s="10">
         <v>1</v>
       </c>
       <c r="F113" s="4">
@@ -4639,30 +4606,30 @@
         <v>0</v>
       </c>
       <c r="H113" s="4">
-        <v>0</v>
-      </c>
-      <c r="I113" s="4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I113" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C114" s="1">
-        <v>5035230</v>
-      </c>
-      <c r="D114" s="10" t="s">
+        <v>2227300</v>
+      </c>
+      <c r="D114" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E114" s="4">
         <v>1</v>
       </c>
       <c r="F114" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="4">
         <v>0</v>
@@ -4676,15 +4643,15 @@
     </row>
     <row r="115" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="C115" s="1">
-        <v>8979506</v>
-      </c>
-      <c r="D115" s="10" t="s">
+        <v>9442269</v>
+      </c>
+      <c r="D115" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E115" s="4">
@@ -4705,18 +4672,18 @@
     </row>
     <row r="116" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="C116" s="1">
-        <v>2486131</v>
-      </c>
-      <c r="D116" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E116" s="4">
+        <v>2227231</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E116" s="10">
         <v>1</v>
       </c>
       <c r="F116" s="4">
@@ -4726,81 +4693,81 @@
         <v>0</v>
       </c>
       <c r="H116" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>96</v>
+        <v>271</v>
       </c>
       <c r="C117" s="1">
-        <v>2486151</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>298</v>
+        <v>5218786</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E117" s="4">
         <v>1</v>
       </c>
       <c r="F117" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="4">
         <v>0</v>
       </c>
       <c r="H117" s="4">
-        <v>0</v>
-      </c>
-      <c r="I117" s="5">
+        <v>1</v>
+      </c>
+      <c r="I117" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C118" s="1">
-        <v>2498305</v>
-      </c>
-      <c r="D118" s="10" t="s">
+      <c r="A118" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C118" s="16">
+        <v>5358460</v>
+      </c>
+      <c r="D118" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="E118" s="4">
-        <v>1</v>
-      </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4">
-        <v>0</v>
-      </c>
-      <c r="H118" s="4">
-        <v>0</v>
-      </c>
-      <c r="I118" s="4">
+      <c r="E118" s="18">
+        <v>1</v>
+      </c>
+      <c r="F118" s="18">
+        <v>0</v>
+      </c>
+      <c r="G118" s="18">
+        <v>0</v>
+      </c>
+      <c r="H118" s="18">
+        <v>0</v>
+      </c>
+      <c r="I118" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>244</v>
+        <v>142</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="C119" s="1">
-        <v>2702865</v>
-      </c>
-      <c r="D119" s="10" t="s">
+        <v>2362868</v>
+      </c>
+      <c r="D119" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E119" s="4">
@@ -4816,56 +4783,56 @@
         <v>0</v>
       </c>
       <c r="I119" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>247</v>
+        <v>47</v>
       </c>
       <c r="C120" s="1">
-        <v>2889088</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E120" s="4">
+        <v>5229055</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E120" s="10">
         <v>1</v>
       </c>
       <c r="F120" s="4">
         <v>0</v>
       </c>
       <c r="G120" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="4">
-        <v>1</v>
-      </c>
-      <c r="I120" s="4">
+        <v>0</v>
+      </c>
+      <c r="I120" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>248</v>
+        <v>50</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>249</v>
+        <v>51</v>
       </c>
       <c r="C121" s="1">
-        <v>3086784</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E121" s="4">
+        <v>2479226</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E121" s="10">
         <v>1</v>
       </c>
       <c r="F121" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="4">
         <v>0</v>
@@ -4873,21 +4840,21 @@
       <c r="H121" s="4">
         <v>0</v>
       </c>
-      <c r="I121" s="4">
+      <c r="I121" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="C122" s="1">
-        <v>2437450</v>
-      </c>
-      <c r="D122" s="10" t="s">
+        <v>2977647</v>
+      </c>
+      <c r="D122" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E122" s="4">
@@ -4908,45 +4875,45 @@
     </row>
     <row r="123" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>97</v>
+        <v>240</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>98</v>
+        <v>241</v>
       </c>
       <c r="C123" s="1">
-        <v>2440954</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>298</v>
+        <v>2486131</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="E123" s="4">
         <v>1</v>
       </c>
-      <c r="F123" s="5">
-        <v>1</v>
-      </c>
-      <c r="G123" s="5">
-        <v>0</v>
-      </c>
-      <c r="H123" s="5">
-        <v>1</v>
-      </c>
-      <c r="I123" s="5">
-        <v>1</v>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0</v>
+      </c>
+      <c r="I123" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>253</v>
+        <v>96</v>
       </c>
       <c r="C124" s="1">
-        <v>6063677</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>299</v>
+        <v>2486151</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E124" s="4">
         <v>1</v>
@@ -4958,23 +4925,23 @@
         <v>0</v>
       </c>
       <c r="H124" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="C125" s="1">
-        <v>5329212</v>
-      </c>
-      <c r="D125" s="10" t="s">
+        <v>4038485</v>
+      </c>
+      <c r="D125" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E125" s="4">
@@ -4984,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="4">
         <v>1</v>
@@ -4995,163 +4962,163 @@
     </row>
     <row r="126" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="C126" s="1">
-        <v>3642949</v>
-      </c>
-      <c r="D126" s="10" t="s">
+        <v>2889173</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E126" s="4">
         <v>1</v>
       </c>
       <c r="F126" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="4">
         <v>1</v>
       </c>
       <c r="I126" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>100</v>
+        <v>247</v>
       </c>
       <c r="C127" s="1">
-        <v>5304257</v>
-      </c>
-      <c r="D127" s="10" t="s">
+        <v>2889088</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4">
+        <v>0</v>
+      </c>
+      <c r="G127" s="4">
+        <v>1</v>
+      </c>
+      <c r="H127" s="4">
+        <v>1</v>
+      </c>
+      <c r="I127" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C128" s="16">
+        <v>3003979</v>
+      </c>
+      <c r="D128" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="E127" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" s="4">
-        <v>1</v>
-      </c>
-      <c r="G127" s="4">
-        <v>0</v>
-      </c>
-      <c r="H127" s="4">
-        <v>0</v>
-      </c>
-      <c r="I127" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C128" s="1">
-        <v>5824863</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E128" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G128" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="H128" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>9</v>
+      <c r="E128" s="20">
+        <v>1</v>
+      </c>
+      <c r="F128" s="21">
+        <v>0</v>
+      </c>
+      <c r="G128" s="20">
+        <v>0</v>
+      </c>
+      <c r="H128" s="20">
+        <v>1</v>
+      </c>
+      <c r="I128" s="20">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>259</v>
+        <v>113</v>
       </c>
       <c r="C129" s="1">
-        <v>3129663</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E129" s="4">
-        <v>1</v>
-      </c>
-      <c r="F129" s="4">
-        <v>0</v>
-      </c>
-      <c r="G129" s="4">
-        <v>0</v>
-      </c>
-      <c r="H129" s="4">
-        <v>0</v>
-      </c>
-      <c r="I129" s="4">
-        <v>0</v>
+        <v>5824863</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="C130" s="1">
-        <v>3054399</v>
-      </c>
-      <c r="D130" s="10" t="s">
+        <v>5274863</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E130" s="4">
         <v>1</v>
       </c>
       <c r="F130" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
       </c>
       <c r="H130" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>262</v>
+        <v>71</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>263</v>
+        <v>72</v>
       </c>
       <c r="C131" s="1">
-        <v>2437399</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E131" s="4">
+        <v>5384932</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E131" s="10">
         <v>1</v>
       </c>
       <c r="F131" s="4">
@@ -5161,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="4">
         <v>0</v>
@@ -5169,15 +5136,15 @@
     </row>
     <row r="132" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="C132" s="1">
-        <v>2489005</v>
-      </c>
-      <c r="D132" s="10" t="s">
+        <v>5219681</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E132" s="4">
@@ -5198,51 +5165,51 @@
     </row>
     <row r="133" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>267</v>
+        <v>127</v>
       </c>
       <c r="C133" s="1">
-        <v>5035187</v>
-      </c>
-      <c r="D133" s="10" t="s">
+        <v>5219683</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E133" s="4">
         <v>1</v>
       </c>
       <c r="F133" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
       </c>
       <c r="H133" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>101</v>
+        <v>266</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>102</v>
+        <v>267</v>
       </c>
       <c r="C134" s="1">
-        <v>8946295</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E134" s="13">
+        <v>5035187</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
       <c r="F134" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="4">
         <v>0</v>
@@ -5256,51 +5223,51 @@
     </row>
     <row r="135" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>103</v>
+        <v>237</v>
       </c>
       <c r="C135" s="1">
-        <v>2865524</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>9</v>
+        <v>5035230</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1</v>
       </c>
       <c r="F135" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="4">
         <v>0</v>
       </c>
       <c r="H135" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C136" s="1">
-        <v>2865565</v>
-      </c>
-      <c r="D136" s="10" t="s">
+        <v>5035017</v>
+      </c>
+      <c r="D136" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E136" s="4">
         <v>1</v>
       </c>
       <c r="F136" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="4">
         <v>0</v>
@@ -5314,57 +5281,57 @@
     </row>
     <row r="137" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="C137" s="1">
-        <v>5218786</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E137" s="4">
+        <v>5389029</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E137" s="10">
         <v>1</v>
       </c>
       <c r="F137" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="4">
         <v>0</v>
       </c>
-      <c r="H137" s="4">
-        <v>1</v>
-      </c>
-      <c r="I137" s="4">
+      <c r="H137" s="10">
+        <v>1</v>
+      </c>
+      <c r="I137" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>272</v>
+        <v>69</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>273</v>
+        <v>70</v>
       </c>
       <c r="C138" s="1">
-        <v>2434552</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E138" s="4">
+        <v>5389017</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E138" s="10">
         <v>1</v>
       </c>
       <c r="F138" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="4">
         <v>0</v>
       </c>
-      <c r="H138" s="4">
-        <v>0</v>
+      <c r="H138" s="10">
+        <v>1</v>
       </c>
       <c r="I138" s="4">
         <v>0</v>
@@ -5372,15 +5339,15 @@
     </row>
     <row r="139" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C139" s="1">
-        <v>5362054</v>
-      </c>
-      <c r="D139" s="10" t="s">
+        <v>2437450</v>
+      </c>
+      <c r="D139" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E139" s="4">
@@ -5393,52 +5360,52 @@
         <v>0</v>
       </c>
       <c r="H139" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>276</v>
+        <v>10</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>277</v>
+        <v>11</v>
       </c>
       <c r="C140" s="1">
-        <v>2765942</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E140" s="4">
-        <v>1</v>
-      </c>
-      <c r="F140" s="4">
-        <v>0</v>
+        <v>2437282</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E140" s="10">
+        <v>1</v>
+      </c>
+      <c r="F140" s="13">
+        <v>1</v>
       </c>
       <c r="G140" s="4">
         <v>0</v>
       </c>
       <c r="H140" s="4">
-        <v>1</v>
-      </c>
-      <c r="I140" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I140" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>278</v>
+        <v>176</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>279</v>
+        <v>177</v>
       </c>
       <c r="C141" s="1">
-        <v>2870583</v>
-      </c>
-      <c r="D141" s="10" t="s">
+        <v>2480764</v>
+      </c>
+      <c r="D141" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E141" s="4">
@@ -5451,23 +5418,23 @@
         <v>0</v>
       </c>
       <c r="H141" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="C142" s="1">
-        <v>5421039</v>
-      </c>
-      <c r="D142" s="10" t="s">
+        <v>2443002</v>
+      </c>
+      <c r="D142" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E142" s="4">
@@ -5480,55 +5447,55 @@
         <v>0</v>
       </c>
       <c r="H142" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="C143" s="1">
-        <v>2882443</v>
-      </c>
-      <c r="D143" s="10" t="s">
+        <v>3054399</v>
+      </c>
+      <c r="D143" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E143" s="4">
         <v>1</v>
       </c>
       <c r="F143" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="4">
         <v>0</v>
       </c>
       <c r="H143" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>285</v>
+        <v>103</v>
       </c>
       <c r="C144" s="1">
-        <v>2350580</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E144" s="4">
+        <v>2865524</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E144" s="10">
         <v>1</v>
       </c>
       <c r="F144" s="4">
@@ -5537,53 +5504,53 @@
       <c r="G144" s="4">
         <v>0</v>
       </c>
-      <c r="H144" s="4">
-        <v>0</v>
-      </c>
-      <c r="I144" s="4">
+      <c r="H144" s="10">
+        <v>1</v>
+      </c>
+      <c r="I144" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="C145" s="1">
-        <v>2978552</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>299</v>
+        <v>5871429</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E145" s="4">
         <v>1</v>
       </c>
       <c r="F145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="4">
         <v>0</v>
       </c>
       <c r="I145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>289</v>
+        <v>135</v>
       </c>
       <c r="C146" s="1">
-        <v>3170247</v>
-      </c>
-      <c r="D146" s="10" t="s">
+        <v>1311477</v>
+      </c>
+      <c r="D146" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E146" s="4">
@@ -5593,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="4">
         <v>0</v>
@@ -5604,28 +5571,28 @@
     </row>
     <row r="147" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="C147" s="1">
-        <v>2394486</v>
-      </c>
-      <c r="D147" s="10" t="s">
+        <v>1315391</v>
+      </c>
+      <c r="D147" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E147" s="4">
         <v>1</v>
       </c>
       <c r="F147" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="4">
         <v>0</v>
       </c>
       <c r="H147" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" s="4">
         <v>1</v>
@@ -5633,15 +5600,15 @@
     </row>
     <row r="148" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>292</v>
+        <v>116</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>293</v>
+        <v>117</v>
       </c>
       <c r="C148" s="1">
-        <v>2340977</v>
-      </c>
-      <c r="D148" s="10" t="s">
+        <v>5217334</v>
+      </c>
+      <c r="D148" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E148" s="4">
@@ -5657,35 +5624,35 @@
         <v>0</v>
       </c>
       <c r="I148" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>295</v>
+        <v>74</v>
       </c>
       <c r="C149" s="1">
-        <v>5035017</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E149" s="4">
+        <v>10919373</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E149" s="10">
         <v>1</v>
       </c>
       <c r="F149" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" s="4">
         <v>0</v>
       </c>
-      <c r="H149" s="4">
-        <v>1</v>
-      </c>
-      <c r="I149" s="4">
+      <c r="H149" s="14">
+        <v>1</v>
+      </c>
+      <c r="I149" s="10">
         <v>1</v>
       </c>
     </row>
@@ -11648,7 +11615,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I149">
-    <sortCondition ref="A2:A149"/>
+    <sortCondition ref="B2:B149"/>
   </sortState>
   <conditionalFormatting sqref="D2:D149">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -11666,8 +11633,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="8"/>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>296</v>
       </c>
     </row>
